--- a/experiments/results/resnet34/CIFAR-10/ASH/adaptive/max/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ASH/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1009,6 +1009,55 @@
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=75,react_th=None,scale_th=4.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=75,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
